--- a/data/Road_fatalities_BG.xlsx
+++ b/data/Road_fatalities_BG.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://xellagroup-my.sharepoint.com/personal/boris_yotsov_xella_com/Documents/U_Drive/Privat/3.PC/Data_Science/12.Project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="92" documentId="11_AD4DF75460589B3ACB728432C71D4FCA5ADEDD97" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{51B01314-DD30-45A3-A3E6-428FBA49C004}"/>
+  <xr:revisionPtr revIDLastSave="93" documentId="11_AD4DF75460589B3ACB728432C71D4FCA5ADEDD97" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4542B8D2-BF15-4683-9C0C-6B5F8922E0A6}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Лист1" sheetId="1" r:id="rId1"/>
+    <sheet name="sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
